--- a/xlsx/技能/普通技能.xlsx
+++ b/xlsx/技能/普通技能.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="技能.aobj.ts" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
   <si>
     <t>id</t>
   </si>
@@ -246,24 +246,6 @@
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>ACcb</t>
-  </si>
-  <si>
-    <t>霜冻闪电</t>
-  </si>
-  <si>
-    <t>ANcl</t>
-  </si>
-  <si>
-    <t>测试闪烁</t>
-  </si>
-  <si>
-    <t>主动6</t>
-  </si>
-  <si>
-    <t>ReplaceableTextures\CommandButtons\BTNBlink.blp</t>
   </si>
 </sst>
 </file>
@@ -1269,12 +1251,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:AC3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
     <col min="6" max="6" width="74.625" customWidth="1"/>
     <col min="7" max="7" width="33.5" customWidth="1"/>
+    <col min="12" max="12" width="16.0833333333333" customWidth="1"/>
     <col min="15" max="15" width="26" customWidth="1"/>
     <col min="22" max="22" width="19.25" customWidth="1"/>
   </cols>
@@ -1540,43 +1523,11 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5"/>
-      <c r="L5">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="P1:AC4 G4:M4 D4:E4 A4 A1:L1 A2:M3" numberStoredAsText="1"/>
+    <ignoredError sqref="P1:AC3 A1:L1 A2:M3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>